--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/atacama.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M200"/>
+  <dimension ref="A1:M202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>14027.41</v>
+        <v>13955.34</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1431.01</v>
+        <v>1416.02</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>784.91</v>
+        <v>776.6900000000001</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1713.44</v>
+        <v>1694.35</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2154.39</v>
+        <v>2142.59</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>744.88</v>
+        <v>740.8</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>746.38</v>
+        <v>745.4299999999999</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>5012.91</v>
+        <v>5030.8</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1102.61</v>
+        <v>1106.55</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1095.89</v>
+        <v>1107.8</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>745.78</v>
+        <v>748.24</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>5497.96</v>
+        <v>5537.6</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>3887.83</v>
+        <v>3871.8</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1725.8</v>
+        <v>1723.13</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>4283.27</v>
+        <v>4276.64</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3057.02</v>
+        <v>3052.28</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1253.77</v>
+        <v>1237.85</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1656.35</v>
+        <v>1635.31</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2001.34</v>
+        <v>1981.43</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2395.16</v>
+        <v>2389.98</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>915.72</v>
+        <v>913.74</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1607.26</v>
+        <v>1603.78</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1877.94</v>
+        <v>1873.88</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>759.47</v>
+        <v>756.28</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1456.83</v>
+        <v>1450.72</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2865.1</v>
+        <v>2853.09</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>14045.63</v>
+        <v>13883.08</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>4537.51</v>
+        <v>4484.99</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1972.07</v>
+        <v>1949.25</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3773.46</v>
+        <v>3729.79</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1671.94</v>
+        <v>1657.78</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>3890.45</v>
+        <v>3857.5</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2145.6</v>
+        <v>2127.43</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>9007.84</v>
+        <v>9031.73</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>3285.26</v>
+        <v>3280.65</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2421.28</v>
+        <v>2417.88</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1381</v>
+        <v>1392.8</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1208.46</v>
+        <v>1215.07</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>11202</v>
+        <v>11263.26</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>811.98</v>
+        <v>816.42</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>3515.99</v>
+        <v>3535.22</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>3927.86</v>
+        <v>3949.34</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>4912.55</v>
+        <v>4939.42</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>826.52</v>
+        <v>807.1900000000001</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2888.29</v>
+        <v>2850.96</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>4285.83</v>
+        <v>4277.39</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1718.84</v>
+        <v>1721.22</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1468.83</v>
+        <v>1470.87</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>869.74</v>
+        <v>881.45</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>5060.61</v>
+        <v>5183.68</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1728.07</v>
+        <v>1771.76</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>795.11</v>
+        <v>819.22</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1570.65</v>
+        <v>1618.27</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1809.28</v>
+        <v>1864.15</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>11669.28</v>
+        <v>12016.12</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1904.02</v>
+        <v>1897.24</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1346.13</v>
+        <v>1336.06</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>5314.84</v>
+        <v>5292.43</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>6329.1</v>
+        <v>6302.42</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>4904.57</v>
+        <v>4883.89</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1904.08</v>
+        <v>1921.4</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>876.77</v>
+        <v>884.75</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2904.23</v>
+        <v>2924.45</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2537.21</v>
+        <v>2554.87</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>821.41</v>
+        <v>826.8200000000001</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>5758.73</v>
+        <v>5796.66</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>6987.44</v>
+        <v>7033.45</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>3491.73</v>
+        <v>3514.73</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>21980.1</v>
+        <v>22175.87</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>966.33</v>
+        <v>974.9400000000001</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>7015.87</v>
+        <v>7078.36</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2693.27</v>
+        <v>2688.65</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1561.32</v>
+        <v>1558.65</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1217.58</v>
+        <v>1208.86</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>915.4400000000001</v>
+        <v>914.1</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2095.47</v>
+        <v>2092.38</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>4518.8</v>
+        <v>4494.19</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1422.89</v>
+        <v>1415.14</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>808.41</v>
+        <v>804</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>6768.07</v>
+        <v>6731.21</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>2299.77</v>
+        <v>2285.79</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>3644.44</v>
+        <v>3647.95</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>27155.18</v>
+        <v>27181.36</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>7306.82</v>
+        <v>7313.86</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1146.99</v>
+        <v>1148.1</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>11226.58</v>
+        <v>11237.39</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>3154.67</v>
+        <v>3157.71</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>7544.2</v>
+        <v>7763.33</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>7647.08</v>
+        <v>7773.12</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>822.45</v>
+        <v>836</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>2222.01</v>
+        <v>2258.63</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>769.2</v>
+        <v>771.09</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>3331.05</v>
+        <v>3339.24</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>987.95</v>
+        <v>990.38</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>3403.46</v>
+        <v>3411.83</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1253.75</v>
+        <v>1256.83</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>45477.95</v>
+        <v>45157.01</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>2037.62</v>
+        <v>2023.24</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>2348.23</v>
+        <v>2390.8</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>982.45</v>
+        <v>997.84</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>5172.44</v>
+        <v>5172.17</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>43835.2</v>
+        <v>43872.96</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>3406.55</v>
+        <v>3367.22</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1350.68</v>
+        <v>1335.09</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>2857.65</v>
+        <v>2815.03</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>769.29</v>
+        <v>764.36</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>19774.92</v>
+        <v>19689.73</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1224.15</v>
+        <v>1206.44</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>3411.57</v>
+        <v>3338.17</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>1269.03</v>
+        <v>1239.5</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>787.25</v>
+        <v>771.72</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>783.8099999999999</v>
+        <v>769.6</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1538.45</v>
+        <v>1510.55</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>798.1799999999999</v>
+        <v>800.51</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>2025.5</v>
+        <v>2031.4</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>2087.18</v>
+        <v>2114.96</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>778.7</v>
+        <v>788.86</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>2885.56</v>
+        <v>2956.57</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>8518.129999999999</v>
+        <v>8679.23</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>11986.67</v>
+        <v>12213.37</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>1551.23</v>
+        <v>1568.88</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>2149.34</v>
+        <v>2173.78</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>799.38</v>
+        <v>808.47</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>901.23</v>
+        <v>911.48</v>
       </c>
     </row>
     <row r="126">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>782.26</v>
+        <v>789.3099999999999</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1172445-62-CM26</t>
+          <t>2609-15-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8159,17 +8159,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>60.902.001-6</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>Departamento Provincial de Educación Copiapo</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.461.733-7</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -8194,13 +8194,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>3119.95</v>
+        <v>923.39</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2609-15-CM26</t>
+          <t>1172445-62-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8220,17 +8220,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>60.902.001-6</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Departamento Provincial de Educación Copiapo</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8240,12 +8240,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>77.461.733-7</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>915.15</v>
+        <v>3148.06</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>786.62</v>
+        <v>789.09</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>1579.87</v>
+        <v>1583.15</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>787.23</v>
+        <v>783.85</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>818.67</v>
+        <v>815.15</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>1928.84</v>
+        <v>1902.62</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>2948.63</v>
+        <v>2923.48</v>
       </c>
     </row>
     <row r="135">
@@ -8682,13 +8682,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>6857.15</v>
+        <v>6933.84</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1554-851-CM26</t>
+          <t>2859-371-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8728,12 +8728,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>2691.17</v>
+        <v>956.84</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2859-371-CM26</t>
+          <t>1554-851-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>953.23</v>
+        <v>2701.37</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>952751-113-CM26</t>
+          <t>952751-112-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8850,12 +8850,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
+          <t>CASTILLA Y ARAGON SPA</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>77.461.733-7</t>
+          <t>96.989.530-7</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -8865,13 +8865,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>802.98</v>
+        <v>1272.75</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>952751-112-CM26</t>
+          <t>952751-113-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>CASTILLA Y ARAGON SPA</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>96.989.530-7</t>
+          <t>77.461.733-7</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>1275.97</v>
+        <v>800.95</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>2064.12</v>
+        <v>2058.91</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>7253.22</v>
+        <v>7322.13</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>2065.25</v>
+        <v>2080.64</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>4964.95</v>
+        <v>5001.94</v>
       </c>
     </row>
     <row r="144">
@@ -9231,13 +9231,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>6029.16</v>
+        <v>6074.08</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1172445-75-CM26</t>
+          <t>1172445-55-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA  E INMOBILIARIA  FORBES  SPA</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.774.294-0</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -9292,13 +9292,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>3511.06</v>
+        <v>1499.05</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1172445-55-CM26</t>
+          <t>1172445-75-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9338,12 +9338,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA  E INMOBILIARIA  FORBES  SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>76.774.294-0</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1505.65</v>
+        <v>3495.67</v>
       </c>
     </row>
     <row r="147">
@@ -9414,13 +9414,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>1468.55</v>
+        <v>1462.11</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2000-18-CM26</t>
+          <t>952751-123-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.923.000-0</t>
+          <t>74.269.600-6</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SERPLAC III Región</t>
+          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9460,12 +9460,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -9475,13 +9475,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>1113.12</v>
+        <v>1539.09</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>952751-123-CM26</t>
+          <t>2000-18-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>74.269.600-6</t>
+          <t>61.923.000-0</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>SERPLAC III Región</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>1542.59</v>
+        <v>1110.59</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>13754.99</v>
+        <v>13721.03</v>
       </c>
     </row>
     <row r="151">
@@ -9658,13 +9658,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>836.6</v>
+        <v>839.26</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2381-642-CM26</t>
+          <t>5350-974-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9684,17 +9684,17 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -9719,13 +9719,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>1840.82</v>
+        <v>1750.06</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2859-442-CM26</t>
+          <t>2381-642-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9750,12 +9750,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>77.461.733-7</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -9780,13 +9780,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>2226.19</v>
+        <v>1850.61</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>5350-974-CM26</t>
+          <t>2859-442-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9806,17 +9806,17 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9826,12 +9826,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.461.733-7</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>1740.81</v>
+        <v>2238.03</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>3934.08</v>
+        <v>3990.37</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>1469.39</v>
+        <v>1490.41</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>4849.97</v>
+        <v>4906.87</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>4580.07</v>
+        <v>4633.8</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>2703.45</v>
+        <v>2735.16</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>3176.52</v>
+        <v>3213.78</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>1506.19</v>
+        <v>1523.86</v>
       </c>
     </row>
     <row r="162">
@@ -10329,13 +10329,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>2212.05</v>
+        <v>2234.54</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2923-434-CM26</t>
+          <t>1172445-121-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10355,17 +10355,17 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -10390,13 +10390,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>808.8</v>
+        <v>2004.68</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1172445-113-CM26</t>
+          <t>2923-434-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10421,12 +10421,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K164" t="inlineStr"/>
@@ -10451,13 +10451,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>5896.77</v>
+        <v>795.14</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1172445-121-CM26</t>
+          <t>1172445-113-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -10497,12 +10497,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>2039.13</v>
+        <v>5797.14</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>3776.61</v>
+        <v>3723.01</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>1109.08</v>
+        <v>1093.84</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>792.85</v>
+        <v>781.95</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>1312</v>
+        <v>1293.97</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>3117.88</v>
+        <v>3075.04</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>2588.67</v>
+        <v>2553.1</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>859.8099999999999</v>
+        <v>854.48</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>2261.04</v>
+        <v>2247.02</v>
       </c>
     </row>
     <row r="174">
@@ -11061,13 +11061,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>1796.49</v>
+        <v>1804.65</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>707416-52-CM26</t>
+          <t>2322-438-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11107,12 +11107,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>VBC GROUP SPA</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.350.794-5</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -11122,13 +11122,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>796.98</v>
+        <v>8740.41</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2322-438-CM26</t>
+          <t>707416-52-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>VBC GROUP SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>77.350.794-5</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
@@ -11183,13 +11183,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>8700.889999999999</v>
+        <v>800.6</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2322-437-CM26</t>
+          <t>1557-202-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11214,12 +11214,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11229,12 +11229,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>TRANSPORTES, LOGÍSTICA Y DISTRIBUCIÓN GROUP SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>77.743.075-0</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K177" t="inlineStr"/>
@@ -11244,13 +11244,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>20435.42</v>
+        <v>2598.74</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1557-202-CM26</t>
+          <t>2322-437-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11275,12 +11275,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11290,12 +11290,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>TRANSPORTES, LOGÍSTICA Y DISTRIBUCIÓN GROUP SPA</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.743.075-0</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>2586.99</v>
+        <v>20528.23</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>3616.31</v>
+        <v>3670.16</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>1119.36</v>
+        <v>1136.03</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>4055.65</v>
+        <v>4083.65</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>7304.4</v>
+        <v>7326.98</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>2330.97</v>
+        <v>2285.35</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>10217.16</v>
+        <v>10017.17</v>
       </c>
     </row>
     <row r="185">
@@ -11732,13 +11732,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>857.45</v>
+        <v>844.75</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>5349-1322-CM26</t>
+          <t>696011-31-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K186" t="inlineStr"/>
@@ -11793,13 +11793,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>1127.26</v>
+        <v>2153.79</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>696011-31-CM26</t>
+          <t>5349-1322-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11824,12 +11824,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K187" t="inlineStr"/>
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>2132.35</v>
+        <v>1138.59</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>1646.17</v>
+        <v>1657.18</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>2522.4</v>
+        <v>2540.05</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>2001.71</v>
+        <v>1997.69</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>1714.67</v>
+        <v>1704.75</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>3656.47</v>
+        <v>3635.31</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>2827.29</v>
+        <v>2810.92</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>2346.11</v>
+        <v>2332.53</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>790.87</v>
+        <v>786.29</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>2590.35</v>
+        <v>2548.54</v>
       </c>
     </row>
     <row r="197">
@@ -12464,13 +12464,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>1683.44</v>
+        <v>1656.45</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1172445-162-CM26</t>
+          <t>411-336-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12495,12 +12495,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12510,12 +12510,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K198" t="inlineStr"/>
@@ -12525,13 +12525,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>1125</v>
+        <v>2956.89</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>411-336-CM26</t>
+          <t>1172445-162-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12556,12 +12556,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>69.251.900-0</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12571,12 +12571,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>2991.7</v>
+        <v>1111.91</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,129 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>1960.53</v>
+        <v>1950.89</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>5349-1672-CM26</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>61.606.303-0</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M201" s="2" t="n">
+        <v>2234.75</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>5349-1762-CM26</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>61.606.303-0</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M202" s="2" t="n">
+        <v>1222.85</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/atacama.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M343"/>
+  <dimension ref="A1:M349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2712,7 +2712,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2923-144-CM25</t>
+          <t>1671-46-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2732,17 +2732,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2752,17 +2752,17 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1937.64</v>
+        <v>1879.7</v>
       </c>
     </row>
     <row r="37">
@@ -2842,7 +2842,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1671-46-CM25</t>
+          <t>2923-144-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2862,17 +2862,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2882,17 +2882,17 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1879.7</v>
+        <v>1937.64</v>
       </c>
     </row>
     <row r="39">
@@ -7962,7 +7962,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1554-1694-CM25</t>
+          <t>707416-110-CM25</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7982,17 +7982,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -8002,28 +8002,32 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>ECOLES SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>77.087.242-1</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>3883.34</v>
+        <v>1148.46</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>707416-110-CM25</t>
+          <t>1554-1694-CM25</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8043,17 +8047,17 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -8063,26 +8067,22 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>ECOLES SPA</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.087.242-1</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1148.46</v>
+        <v>3883.34</v>
       </c>
     </row>
     <row r="120">
@@ -8470,7 +8470,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>707416-120-CM25</t>
+          <t>1172445-2336-CM25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8510,32 +8510,28 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA  E INMOBILIARIA  FORBES  SPA</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.774.294-0</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>2331.55</v>
+        <v>1459.58</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1172445-2336-CM25</t>
+          <t>707416-120-CM25</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8560,12 +8556,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8575,22 +8571,26 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA  E INMOBILIARIA  FORBES  SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>76.774.294-0</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1459.58</v>
+        <v>2331.55</v>
       </c>
     </row>
     <row r="128">
@@ -10193,7 +10193,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2926-342-CM25</t>
+          <t>1554-1991-CM25</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10218,12 +10218,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -10233,26 +10233,22 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA  E INMOBILIARIA  FORBES  SPA</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.774.294-0</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>3729.79</v>
+        <v>1949.25</v>
       </c>
     </row>
     <row r="154">
@@ -10388,7 +10384,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1554-1991-CM25</t>
+          <t>2926-342-CM25</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10413,12 +10409,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10428,22 +10424,26 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA  E INMOBILIARIA  FORBES  SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>76.774.294-0</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>1949.25</v>
+        <v>3729.79</v>
       </c>
     </row>
     <row r="157">
@@ -12123,7 +12123,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2175-12-CM26</t>
+          <t>1557-39-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12143,17 +12143,17 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -12163,17 +12163,17 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -12182,7 +12182,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>5292.43</v>
+        <v>4883.89</v>
       </c>
     </row>
     <row r="184">
@@ -12249,7 +12249,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1557-39-CM26</t>
+          <t>2175-12-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12269,17 +12269,17 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -12289,17 +12289,17 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -12308,7 +12308,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>4883.89</v>
+        <v>5292.43</v>
       </c>
     </row>
     <row r="186">
@@ -12574,7 +12574,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1172445-7-CM26</t>
+          <t>3703-97-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.700-6</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12633,13 +12633,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>7033.45</v>
+        <v>3514.73</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>3703-97-CM26</t>
+          <t>1176812-5-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>69.030.700-6</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUASCO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12679,32 +12679,28 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA  E INMOBILIARIA  FORBES  SPA</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.774.294-0</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>3514.73</v>
+        <v>826.8200000000001</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1176812-5-CM26</t>
+          <t>1172445-6-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12744,28 +12740,32 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA  E INMOBILIARIA  FORBES  SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>76.774.294-0</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>826.8200000000001</v>
+        <v>5796.66</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1172445-6-CM26</t>
+          <t>1172445-7-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12824,7 +12824,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>5796.66</v>
+        <v>7033.45</v>
       </c>
     </row>
     <row r="194">
@@ -13021,7 +13021,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>3281-18-CM26</t>
+          <t>5349-362-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -13046,12 +13046,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -13061,17 +13061,17 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -13080,13 +13080,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>2688.65</v>
+        <v>1558.65</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>5349-362-CM26</t>
+          <t>3281-18-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -13126,17 +13126,17 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -13145,7 +13145,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>1558.65</v>
+        <v>2688.65</v>
       </c>
     </row>
     <row r="199">
@@ -13216,7 +13216,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>4355-142-CM26</t>
+          <t>1346283-24-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -13241,12 +13241,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -13275,13 +13275,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>2092.38</v>
+        <v>914.1</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1346283-24-CM26</t>
+          <t>4355-142-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -13306,12 +13306,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -13340,13 +13340,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>914.1</v>
+        <v>2092.38</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>4355-154-CM26</t>
+          <t>411-76-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -13366,17 +13366,17 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -13405,13 +13405,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>804</v>
+        <v>4494.19</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>411-76-CM26</t>
+          <t>4355-154-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -13431,17 +13431,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>69.251.900-0</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -13470,7 +13470,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>4494.19</v>
+        <v>804</v>
       </c>
     </row>
     <row r="204">
@@ -13606,7 +13606,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1176812-16-CM26</t>
+          <t>2381-249-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13631,12 +13631,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13646,28 +13646,32 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA  E INMOBILIARIA  FORBES  SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>76.774.294-0</t>
-        </is>
-      </c>
-      <c r="K206" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>3647.95</v>
+        <v>3157.71</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1172445-12-CM26</t>
+          <t>1171166-35-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13707,17 +13711,17 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -13726,7 +13730,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>27181.36</v>
+        <v>1148.1</v>
       </c>
     </row>
     <row r="208">
@@ -13793,7 +13797,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1171166-35-CM26</t>
+          <t>1172445-12-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13833,17 +13837,17 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -13852,13 +13856,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>1148.1</v>
+        <v>27181.36</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1172445-13-CM26</t>
+          <t>1176812-16-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13913,13 +13917,13 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>11237.39</v>
+        <v>3647.95</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2381-249-CM26</t>
+          <t>1172445-13-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13944,12 +13948,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13959,26 +13963,22 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA  E INMOBILIARIA  FORBES  SPA</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.774.294-0</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>3157.71</v>
+        <v>11237.39</v>
       </c>
     </row>
     <row r="212">
@@ -14049,7 +14049,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>904-16-CM26</t>
+          <t>1172445-21-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -14074,12 +14074,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -14089,17 +14089,17 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -14108,13 +14108,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>836</v>
+        <v>7773.12</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1171166-65-CM26</t>
+          <t>904-16-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -14139,12 +14139,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -14173,13 +14173,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>2258.63</v>
+        <v>836</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1172445-21-CM26</t>
+          <t>1171166-65-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -14219,17 +14219,17 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -14238,7 +14238,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>7773.12</v>
+        <v>2258.63</v>
       </c>
     </row>
     <row r="216">
@@ -14752,7 +14752,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1376-172-CM26</t>
+          <t>1554-424-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14777,12 +14777,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14792,32 +14792,28 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA  E INMOBILIARIA  FORBES  SPA</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.774.294-0</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr"/>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>1335.09</v>
+        <v>3367.22</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1554-424-CM26</t>
+          <t>1376-172-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14842,12 +14838,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14857,22 +14853,26 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA  E INMOBILIARIA  FORBES  SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>76.774.294-0</t>
-        </is>
-      </c>
-      <c r="K225" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>3367.22</v>
+        <v>1335.09</v>
       </c>
     </row>
     <row r="226">
@@ -15333,7 +15333,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>4357-97-CM26</t>
+          <t>5349-641-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -15353,17 +15353,17 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -15373,17 +15373,17 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -15392,13 +15392,13 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>769.6</v>
+        <v>1510.55</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>5349-641-CM26</t>
+          <t>4357-97-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -15418,17 +15418,17 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -15438,17 +15438,17 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -15457,7 +15457,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>1510.55</v>
+        <v>769.6</v>
       </c>
     </row>
     <row r="235">
@@ -15788,7 +15788,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1172445-53-CM26</t>
+          <t>1172445-54-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15847,13 +15847,13 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>8679.23</v>
+        <v>12213.37</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1172445-54-CM26</t>
+          <t>1172445-53-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15912,13 +15912,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>12213.37</v>
+        <v>8679.23</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1172445-57-CM26</t>
+          <t>1172445-60-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15958,17 +15958,17 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>OTTO HAN SPA</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>77.809.872-5</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -15977,13 +15977,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>2173.78</v>
+        <v>808.47</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1172445-60-CM26</t>
+          <t>1172445-61-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -16023,17 +16023,17 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>OTTO HAN SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>77.809.872-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -16042,13 +16042,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>808.47</v>
+        <v>911.48</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1172445-61-CM26</t>
+          <t>1172445-57-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -16088,17 +16088,17 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -16107,7 +16107,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>911.48</v>
+        <v>2173.78</v>
       </c>
     </row>
     <row r="245">
@@ -16243,7 +16243,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1172445-62-CM26</t>
+          <t>2609-15-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -16268,12 +16268,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>60.902.001-6</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -16283,17 +16283,17 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.461.733-7</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -16302,13 +16302,13 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>3148.06</v>
+        <v>923.39</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2609-15-CM26</t>
+          <t>1172445-62-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -16333,12 +16333,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>60.902.001-6</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -16348,17 +16348,17 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>77.461.733-7</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -16367,7 +16367,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>923.39</v>
+        <v>3148.06</v>
       </c>
     </row>
     <row r="249">
@@ -16828,7 +16828,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2859-371-CM26</t>
+          <t>1554-851-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16853,12 +16853,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16868,12 +16868,12 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -16887,13 +16887,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>956.84</v>
+        <v>2701.37</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1554-851-CM26</t>
+          <t>2859-371-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16918,12 +16918,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16933,12 +16933,12 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -16952,7 +16952,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>2701.37</v>
+        <v>956.84</v>
       </c>
     </row>
     <row r="258">
@@ -17657,7 +17657,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2381-642-CM26</t>
+          <t>2859-442-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -17682,12 +17682,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -17697,17 +17697,17 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.461.733-7</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -17716,13 +17716,13 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>1850.61</v>
+        <v>2238.03</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2859-442-CM26</t>
+          <t>2381-642-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -17747,12 +17747,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -17762,17 +17762,17 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>77.461.733-7</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -17781,13 +17781,13 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>2238.03</v>
+        <v>1850.61</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1172445-94-CM26</t>
+          <t>1172445-95-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -17827,17 +17827,17 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -17846,13 +17846,13 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>3990.37</v>
+        <v>1490.41</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1172445-95-CM26</t>
+          <t>1172445-94-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17892,17 +17892,17 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -17911,7 +17911,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>1490.41</v>
+        <v>3990.37</v>
       </c>
     </row>
     <row r="273">
@@ -18238,7 +18238,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>1172445-121-CM26</t>
+          <t>1172445-113-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -18278,17 +18278,17 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
@@ -18297,13 +18297,13 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>2004.68</v>
+        <v>5797.14</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2923-434-CM26</t>
+          <t>1172445-121-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -18323,17 +18323,17 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -18343,12 +18343,12 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
@@ -18362,13 +18362,13 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>795.14</v>
+        <v>2004.68</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>1172445-113-CM26</t>
+          <t>2923-434-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -18388,17 +18388,17 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -18408,17 +18408,17 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -18427,7 +18427,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>5797.14</v>
+        <v>795.14</v>
       </c>
     </row>
     <row r="281">
@@ -18494,7 +18494,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>904-70-CM26</t>
+          <t>3281-47-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18514,17 +18514,17 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -18534,17 +18534,17 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -18553,13 +18553,13 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>1093.84</v>
+        <v>3075.04</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>1376-388-CM26</t>
+          <t>3281-48-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -18584,12 +18584,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -18599,17 +18599,17 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>OTTO HAN SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>77.809.872-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -18618,13 +18618,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>781.95</v>
+        <v>2553.1</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1376-389-CM26</t>
+          <t>1376-388-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18664,12 +18664,12 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>OTTO HAN SPA</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.809.872-5</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
@@ -18683,13 +18683,13 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>1293.97</v>
+        <v>781.95</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>3281-47-CM26</t>
+          <t>1376-389-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18714,12 +18714,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -18729,12 +18729,12 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
@@ -18748,13 +18748,13 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>3075.04</v>
+        <v>1293.97</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>3281-48-CM26</t>
+          <t>904-70-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -18774,17 +18774,17 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -18813,7 +18813,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>2553.1</v>
+        <v>1093.84</v>
       </c>
     </row>
     <row r="287">
@@ -18949,7 +18949,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2322-437-CM26</t>
+          <t>5349-1180-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -18974,12 +18974,12 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -18989,17 +18989,17 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>TRANSPORTES, LOGÍSTICA Y DISTRIBUCIÓN GROUP SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>77.743.075-0</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
@@ -19008,13 +19008,13 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>20528.23</v>
+        <v>1804.65</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>5349-1180-CM26</t>
+          <t>2322-438-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -19039,12 +19039,12 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -19054,17 +19054,17 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>VBC GROUP SPA</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.350.794-5</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
@@ -19073,7 +19073,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>1804.65</v>
+        <v>8740.41</v>
       </c>
     </row>
     <row r="291">
@@ -19209,7 +19209,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2322-438-CM26</t>
+          <t>2322-437-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -19249,12 +19249,12 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>VBC GROUP SPA</t>
+          <t>TRANSPORTES, LOGÍSTICA Y DISTRIBUCIÓN GROUP SPA</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>77.350.794-5</t>
+          <t>77.743.075-0</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
@@ -19268,7 +19268,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>8740.41</v>
+        <v>20528.23</v>
       </c>
     </row>
     <row r="294">
@@ -19725,7 +19725,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>696011-31-CM26</t>
+          <t>5349-1322-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -19745,17 +19745,17 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -19765,17 +19765,17 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
@@ -19784,13 +19784,13 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>2153.79</v>
+        <v>1138.59</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>5349-1322-CM26</t>
+          <t>696011-31-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -19810,17 +19810,17 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -19830,17 +19830,17 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
@@ -19849,7 +19849,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>1138.59</v>
+        <v>2153.79</v>
       </c>
     </row>
     <row r="303">
@@ -20050,7 +20050,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>1176812-66-CM26</t>
+          <t>846-95-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -20070,17 +20070,17 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -20090,17 +20090,17 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -20109,13 +20109,13 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>1704.75</v>
+        <v>2332.53</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>5350-1183-CM26</t>
+          <t>846-96-CM26</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -20140,12 +20140,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -20155,17 +20155,17 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.461.733-7</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
@@ -20174,7 +20174,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>3635.31</v>
+        <v>786.29</v>
       </c>
     </row>
     <row r="308">
@@ -20245,7 +20245,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>846-95-CM26</t>
+          <t>1176812-66-CM26</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -20265,17 +20265,17 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -20285,17 +20285,17 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>2332.53</v>
+        <v>1704.75</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>846-96-CM26</t>
+          <t>5350-1183-CM26</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -20335,12 +20335,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -20350,17 +20350,17 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>77.461.733-7</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
@@ -20369,7 +20369,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>786.29</v>
+        <v>3635.31</v>
       </c>
     </row>
     <row r="311">
@@ -20505,7 +20505,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>1172445-162-CM26</t>
+          <t>411-336-CM26</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -20530,12 +20530,12 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -20545,17 +20545,17 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
@@ -20564,13 +20564,13 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>1111.91</v>
+        <v>2956.89</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>411-336-CM26</t>
+          <t>1172445-162-CM26</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -20595,12 +20595,12 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>69.251.900-0</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -20610,17 +20610,17 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
@@ -20629,7 +20629,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>2956.89</v>
+        <v>1111.91</v>
       </c>
     </row>
     <row r="315">
@@ -21545,7 +21545,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2381-1224-CM26</t>
+          <t>651-159-CM26</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -21565,17 +21565,17 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>69.030.200-4</t>
+          <t>61.815.000-3</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COPIAPO</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -21585,17 +21585,17 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
@@ -21604,13 +21604,13 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>2767.59</v>
+        <v>1291.29</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>651-159-CM26</t>
+          <t>2381-1224-CM26</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -21630,17 +21630,17 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>61.815.000-3</t>
+          <t>69.030.200-4</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -21650,17 +21650,17 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
@@ -21669,7 +21669,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>1291.29</v>
+        <v>2767.59</v>
       </c>
     </row>
     <row r="331">
@@ -21825,7 +21825,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
@@ -21870,7 +21870,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>5350-1507-CM26</t>
+          <t>5350-1508-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -21910,17 +21910,17 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
@@ -21929,13 +21929,13 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>786.52</v>
+        <v>1072.91</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>5350-1508-CM26</t>
+          <t>5350-1507-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -21975,17 +21975,17 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
@@ -21994,7 +21994,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>1072.91</v>
+        <v>786.52</v>
       </c>
     </row>
     <row r="336">
@@ -22020,7 +22020,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
@@ -22065,7 +22065,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>1172445-173-CM26</t>
+          <t>707416-85-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -22090,12 +22090,12 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -22124,13 +22124,13 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>4701.56</v>
+        <v>1879.76</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>1172445-174-CM26</t>
+          <t>1171166-225-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -22185,13 +22185,13 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>1486.21</v>
+        <v>1366.12</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>1171166-225-CM26</t>
+          <t>1172445-173-CM26</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -22211,7 +22211,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
@@ -22231,28 +22231,32 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA  E INMOBILIARIA  FORBES  SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>76.774.294-0</t>
-        </is>
-      </c>
-      <c r="K339" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>1366.12</v>
+        <v>4701.56</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>707416-85-CM26</t>
+          <t>1172445-174-CM26</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -22272,17 +22276,17 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -22292,32 +22296,28 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA  E INMOBILIARIA  FORBES  SPA</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K340" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.774.294-0</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr"/>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>1879.76</v>
+        <v>1486.21</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>696011-60-CM26</t>
+          <t>1172445-201-CM26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -22337,17 +22337,17 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -22357,12 +22357,12 @@
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
@@ -22376,13 +22376,13 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>1554.61</v>
+        <v>914.33</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>1172445-201-CM26</t>
+          <t>5349-1971-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -22402,17 +22402,17 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -22422,17 +22422,17 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
@@ -22441,13 +22441,13 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>914.33</v>
+        <v>1833.48</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>5349-1971-CM26</t>
+          <t>696011-60-CM26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -22472,12 +22472,12 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -22487,26 +22487,412 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M343" s="2" t="n">
+        <v>1554.61</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>1376-720-CM26</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>61.004.010-1</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
           <t>DIMERC S A</t>
         </is>
       </c>
-      <c r="J343" t="inlineStr">
+      <c r="J344" t="inlineStr">
         <is>
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr">
+      <c r="K344" t="inlineStr">
         <is>
           <t>Antofagasta</t>
         </is>
       </c>
-      <c r="L343" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M343" s="2" t="n">
-        <v>1833.48</v>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M344" s="2" t="n">
+        <v>876.05</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>1353-27-CM26</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>61.002.009-7</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>76.213.681-3</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M345" s="2" t="n">
+        <v>748.1</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>700-37-CM26</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>60.703.000-6</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M346" s="2" t="n">
+        <v>1166.97</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>651-169-CM26</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>61.815.000-3</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>IMPORTADORA  Y DISTRIBUIDORA BLANMAR SPA</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>76.993.355-7</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr"/>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M347" s="2" t="n">
+        <v>1016.85</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2381-1340-CM26</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>69.030.200-4</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COPIAPO</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M348" s="2" t="n">
+        <v>3721.24</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>1558-375-CM26</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>61.606.306-5</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M349" s="2" t="n">
+        <v>1278.53</v>
       </c>
     </row>
   </sheetData>
